--- a/Content-Marketing/Course-Level/Content-Marketing-Course-Outline.xlsx
+++ b/Content-Marketing/Course-Level/Content-Marketing-Course-Outline.xlsx
@@ -535,12 +535,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>cm-template-kompetitor.txt (atau cm-profil-dapur-rara.txt sebagai contoh)</t>
+          <t>cm-template-kompetitor.txt (sudah terisi contoh Dapur Rara, edit untuk bisnis sendiri)</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Isi template dengan data 3 kompetitor nyata, termasuk palet warna dan mood/gaya visual. Minta Claude buat SWOT + gap + 3 variasi kalimat positioning. Simpan 1 di Claude Projects untuk dipakai di Modul 2-5.</t>
+          <t>Pakai contoh Dapur Rara langsung, atau ganti dulu isinya dengan data bisnis + 3 kompetitor nyata (termasuk palet warna dan mood/gaya visual). Paste ke Claude, minta SWOT + gap + 3 variasi kalimat positioning. Simpan 1 di Claude Projects untuk dipakai di Modul 2-5.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">

--- a/Content-Marketing/Course-Level/Content-Marketing-Course-Outline.xlsx
+++ b/Content-Marketing/Course-Level/Content-Marketing-Course-Outline.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Pakai contoh Dapur Rara langsung, atau ganti dulu isinya dengan data bisnis + 3 kompetitor nyata (termasuk palet warna dan mood/gaya visual). Paste ke Claude, minta SWOT + gap + 3 variasi kalimat positioning. Simpan 1 di Claude Projects untuk dipakai di Modul 2-5.</t>
+          <t>Pakai contoh Dapur Rara langsung, atau ganti dulu Data Bisnis + Data Kompetitor di dalamnya (termasuk palet warna dan mood/gaya visual). Copy bagian yang ditandai PASTE KE CLAUDE saja (bukan seluruh file) ke Claude, minta SWOT + gap + 3 variasi kalimat positioning. Simpan 1 di Claude Projects untuk dipakai di Modul 2-5.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">

--- a/Content-Marketing/Course-Level/Content-Marketing-Course-Outline.xlsx
+++ b/Content-Marketing/Course-Level/Content-Marketing-Course-Outline.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Membuat deskripsi produk marketplace yang SEO-friendly dan menjual, pakai positioning dari Modul 1 sebagai acuan.</t>
+          <t>Membuat deskripsi produk marketplace yang SEO-friendly dan menjual. Data produk disimpan di Project Knowledge yang sama dengan positioning Modul 1, jadi otomatis dipakai lagi di Modul 3-5.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -580,7 +580,7 @@
           <t>- Struktur deskripsi produk yang menjual (hook, keyword, spesifikasi, benefit vs fitur, CTA)
 - Kesalahan umum (copy dari supplier, fokus fitur teknis, tanpa keyword, terlalu panjang tanpa struktur)
 - Contoh prompt buruk vs baik
-- Cara kerja 5 langkah: isi CSV -&gt; upload ke Claude -&gt; tambah positioning + instruksi format -&gt; review keyword -&gt; paste &amp; track ranking</t>
+- Cara kerja 5 langkah: isi CSV -&gt; upload ke Project Knowledge (bukan cuma chat) -&gt; generate langsung (positioning &amp; data produk otomatis dari Project) -&gt; review keyword -&gt; paste &amp; track ranking</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -590,12 +590,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Isi CSV minimal 5 produk. Upload ke Claude, generate semua deskripsi sekaligus. Paste 1 deskripsi terbaik ke listing, cek ranking setelah 7 hari.</t>
+          <t>Isi CSV minimal 5 produk. Upload ke Project Knowledge dari Project yang sama dengan Modul 1, generate semua deskripsi sekaligus tanpa ketik ulang positioning. Paste 1 deskripsi terbaik ke listing, cek ranking setelah 7 hari.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Claude.ai (chat + upload CSV), Tokopedia/Shopee (paste manual)</t>
+          <t>Claude.ai (chat), Claude Projects (Project Knowledge: cm-data-produk.csv), Tokopedia/Shopee (paste manual)</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Membangun sistem kalender konten Instagram 30 hari dalam 1 sesi, pakai positioning + daftar produk sebagai bahan. Termasuk setup Canva Connector dan opsi Claude membuat grafis sederhana langsung.</t>
+          <t>Membangun sistem kalender konten Instagram 30 hari dalam 1 sesi — positioning dan katalog produk sudah otomatis tersedia dari Project yang sama (Modul 1-2). Termasuk setup Canva Connector dan opsi Claude membuat grafis sederhana langsung.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Claude.ai (chat), Canva Connector, Claude Projects (baca positioning + identitas visual dari Modul 1)</t>
+          <t>Claude.ai (chat), Canva Connector, Claude Projects (baca positioning dari Modul 1 + katalog produk dari Modul 2, keduanya otomatis)</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">

--- a/Content-Marketing/Course-Level/Content-Marketing-Course-Outline.xlsx
+++ b/Content-Marketing/Course-Level/Content-Marketing-Course-Outline.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Isi CSV minimal 5 produk. Upload ke Project Knowledge dari Project yang sama dengan Modul 1, generate semua deskripsi sekaligus tanpa ketik ulang positioning. Paste 1 deskripsi terbaik ke listing, cek ranking setelah 7 hari.</t>
+          <t>Isi CSV minimal 5 produk. Upload ke Project Knowledge dari Project yang sama dengan Modul 1, lalu jalankan prompt siap-pakai di halaman kursus (copy-paste, sudah termasuk instruksi format). Paste 1 deskripsi terbaik ke listing, cek ranking setelah 7 hari.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Generate kalender konten Instagram 30 hari (16 post/bulan) dari positioning + daftar produk. Setup Canva Connector, buat 2-3 desain. Isi ke cm-kalender-konten.csv, jadwalkan minggu pertama.</t>
+          <t>Jalankan prompt siap-pakai di halaman kursus untuk generate kalender Instagram 30 hari (16 post/bulan) dari positioning + daftar produk yang sudah ada di Project. Setup Canva Connector, buat 2-3 desain. Isi ke cm-kalender-konten.csv, jadwalkan minggu pertama.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Buat 3 variasi copy iklan untuk 1 promo/produk di platform pilihan. Minta Claude buatkan desain Canva sesuai brand. Jalankan A/B test 3 hari, track CTR dan ROAS.</t>
+          <t>Jalankan prompt siap-pakai di halaman kursus (ganti [nama produk/promo], [diskon], dll dengan datamu) untuk 1 promo/produk di platform pilihan. Minta Claude buatkan desain Canva sesuai brand. Jalankan A/B test 3 hari, track CTR dan ROAS.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Tambahkan brand voice CS ke Claude Project dari Modul 1. Buat 10 template WhatsApp untuk skenario umum + minimal 2 draft email via Gmail Connector.</t>
+          <t>Jalankan prompt siap-pakai di halaman kursus untuk tambahkan brand voice CS ke Claude Project dari Modul 1, generate 10 template WhatsApp + 2 draft email sekaligus via Gmail Connector.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
